--- a/questionnaire_templates/028_pet_owner_preventive_care_habits_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/028_pet_owner_preventive_care_habits_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="46" customWidth="1" min="2" max="2"/>
-    <col width="46" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_'2-1',_'label':_'dog'}</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': '2-1', 'label': 'Dog'}</t>
+          <t>Dog</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_'2-2',_'label':_'cat'}</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': '2-2', 'label': 'Cat'}</t>
+          <t>Cat</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_'2-3',_'label':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': '2-3', 'label': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_'3-1',_'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': '3-1', 'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_'3-2',_'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': '3-2', 'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_'3-3',_'label':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': '3-3', 'label': 'Monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_'3-4',_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': '3-4', 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_'7-1',_'label':_'regular'}</t>
+          <t>regular</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': '7-1', 'label': 'Regular'}</t>
+          <t>Regular</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_'7-2',_'label':_'as_needed'}</t>
+          <t>as_needed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': '7-2', 'label': 'As needed'}</t>
+          <t>As needed</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_'7-3',_'label':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': '7-3', 'label': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_'8-1',_'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': '8-1', 'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_'8-2',_'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': '8-2', 'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_'8-3',_'label':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': '8-3', 'label': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_'8-4',_'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': '8-4', 'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_'9-1',_'label':_'every_6_months'}</t>
+          <t>every_6_months</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': '9-1', 'label': 'Every 6 months'}</t>
+          <t>Every 6 months</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_'9-2',_'label':_'every_12_months'}</t>
+          <t>every_12_months</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': '9-2', 'label': 'Every 12 months'}</t>
+          <t>Every 12 months</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_'9-3',_'label':_'more_than_6_months'}</t>
+          <t>more_than_6_months</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': '9-3', 'label': 'More than 6 months'}</t>
+          <t>More than 6 months</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_'10-1',_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': '10-1', 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_'10-2',_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': '10-2', 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_'10-3',_'label':_'undecided'}</t>
+          <t>undecided</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': '10-3', 'label': 'Undecided'}</t>
+          <t>Undecided</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_'11-1',_'label':_'dog'}</t>
+          <t>dog</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': '11-1', 'label': 'Dog'}</t>
+          <t>Dog</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_'11-2',_'label':_'cat'}</t>
+          <t>cat</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': '11-2', 'label': 'Cat'}</t>
+          <t>Cat</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_'11-3',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': '11-3', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
